--- a/src/Portafolio_de_Proyectos_2026 (2).xlsx
+++ b/src/Portafolio_de_Proyectos_2026 (2).xlsx
@@ -5,11 +5,11 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6120" tabRatio="801"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6120" tabRatio="801" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Portafolio P&amp;D" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cuenta DNI (Cloud)'!$A$1:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Demanda Estrategica CT'!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pys Transf Digital'!$B$3:$BO$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pys Transf Digital'!$B$3:$BO$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pys Transf Digital'!$A$1:$BO$36</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4815" uniqueCount="1490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="1493">
   <si>
     <t>N°</t>
   </si>
@@ -6034,6 +6034,15 @@
   <si>
     <t>Últ. Estado CQ 17.03</t>
   </si>
+  <si>
+    <t>2025-T0820</t>
+  </si>
+  <si>
+    <t>NUEVOOOOOOOOOOOOOOOOOOOOOOO</t>
+  </si>
+  <si>
+    <t>BID-C1</t>
+  </si>
 </sst>
 </file>
 
@@ -6045,7 +6054,7 @@
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6441,6 +6450,13 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1923EB"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -7528,7 +7544,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="541">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -9161,6 +9177,72 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="14" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -9207,10 +9289,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9219,7 +9297,7 @@
     <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="179">
+  <dxfs count="180">
     <dxf>
       <font>
         <b val="0"/>
@@ -12477,6 +12555,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <strike val="0"/>
         <outline val="0"/>
@@ -13489,7 +13577,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 2" pivot="0" count="1">
-      <tableStyleElement type="wholeTable" dxfId="178"/>
+      <tableStyleElement type="wholeTable" dxfId="179"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -13932,48 +14020,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="A2:AE43" totalsRowShown="0" headerRowDxfId="177" dataDxfId="176">
-  <autoFilter ref="A2:AE43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="A2:AE43" totalsRowShown="0" headerRowDxfId="178" dataDxfId="177">
+  <autoFilter ref="A2:AE43">
+    <filterColumn colId="21">
+      <filters>
+        <filter val="BID"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="31">
-    <tableColumn id="1" name="N°" dataDxfId="175"/>
-    <tableColumn id="2" name="Código de Planeamiento" dataDxfId="174"/>
-    <tableColumn id="4" name="Nombre del Proyecto" dataDxfId="173"/>
-    <tableColumn id="5" name="Alcance del Proyecto" dataDxfId="172"/>
-    <tableColumn id="16391" name="Gerencia Líder" dataDxfId="171"/>
-    <tableColumn id="16390" name="Líder del Proyecto" dataDxfId="170"/>
-    <tableColumn id="16389" name="Usuario Funcional" dataDxfId="169"/>
-    <tableColumn id="16408" name="Gestor de Planeamiento" dataDxfId="168"/>
-    <tableColumn id="16401" name="Presupuesto asignado" dataDxfId="167"/>
-    <tableColumn id="7" name="Valor Ganado (EV)" dataDxfId="166">
+    <tableColumn id="1" name="N°" dataDxfId="176"/>
+    <tableColumn id="2" name="Código de Planeamiento" dataDxfId="175"/>
+    <tableColumn id="4" name="Nombre del Proyecto" dataDxfId="174"/>
+    <tableColumn id="5" name="Alcance del Proyecto" dataDxfId="173"/>
+    <tableColumn id="16391" name="Gerencia Líder" dataDxfId="172"/>
+    <tableColumn id="16390" name="Líder del Proyecto" dataDxfId="171"/>
+    <tableColumn id="16389" name="Usuario Funcional" dataDxfId="170"/>
+    <tableColumn id="16408" name="Gestor de Planeamiento" dataDxfId="169"/>
+    <tableColumn id="16401" name="Presupuesto asignado" dataDxfId="168"/>
+    <tableColumn id="7" name="Valor Ganado (EV)" dataDxfId="167">
       <calculatedColumnFormula>Tabla3[[#This Row],[Presupuesto asignado]]/2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Costo Actual (AC)" dataDxfId="165">
+    <tableColumn id="6" name="Costo Actual (AC)" dataDxfId="166">
       <calculatedColumnFormula>Tabla3[[#This Row],[Valor Ganado (EV)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="CPI" dataDxfId="164">
+    <tableColumn id="3" name="CPI" dataDxfId="165">
       <calculatedColumnFormula>Tabla3[[#This Row],[Valor Ganado (EV)]]/Tabla3[[#This Row],[Costo Actual (AC)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16399" name="Fecha Comité Ejec. Proy." dataDxfId="163"/>
-    <tableColumn id="16400" name="N° Acta Comité_x000a_(aprobación)" dataDxfId="162"/>
-    <tableColumn id="16404" name="Dimensión" dataDxfId="161"/>
-    <tableColumn id="16405" name="Objetivo" dataDxfId="160"/>
-    <tableColumn id="16403" name="Año Inicio Planificado" dataDxfId="159"/>
-    <tableColumn id="16402" name="Año Fin Planificado" dataDxfId="158"/>
-    <tableColumn id="16406" name="N° Solicitudes de cambio" dataDxfId="157"/>
-    <tableColumn id="16409" name="Componente Tecnológico" dataDxfId="156"/>
-    <tableColumn id="16407" name="Transformación Digital" dataDxfId="155"/>
-    <tableColumn id="16394" name="Cartera" dataDxfId="154"/>
-    <tableColumn id="18" name="Anexo 1 _x000a_(Modelo de Negocio)" dataDxfId="153"/>
-    <tableColumn id="20" name="Líder Técnico" dataDxfId="152"/>
-    <tableColumn id="21" name="Fecha Inicio" dataDxfId="151"/>
-    <tableColumn id="22" name="Fecha Fin" dataDxfId="150"/>
-    <tableColumn id="23" name="% Avance Planificado" dataDxfId="149"/>
-    <tableColumn id="24" name="% Avance ejecutado" dataDxfId="148"/>
-    <tableColumn id="25" name="Desv. %" dataDxfId="147">
+    <tableColumn id="16399" name="Fecha Comité Ejec. Proy." dataDxfId="164"/>
+    <tableColumn id="16400" name="N° Acta Comité_x000a_(aprobación)" dataDxfId="163"/>
+    <tableColumn id="16404" name="Dimensión" dataDxfId="162"/>
+    <tableColumn id="16405" name="Objetivo" dataDxfId="161"/>
+    <tableColumn id="16403" name="Año Inicio Planificado" dataDxfId="160"/>
+    <tableColumn id="16402" name="Año Fin Planificado" dataDxfId="159"/>
+    <tableColumn id="16406" name="N° Solicitudes de cambio" dataDxfId="158"/>
+    <tableColumn id="16409" name="Componente Tecnológico" dataDxfId="157"/>
+    <tableColumn id="16407" name="Transformación Digital" dataDxfId="156"/>
+    <tableColumn id="16394" name="Cartera" dataDxfId="155"/>
+    <tableColumn id="18" name="Anexo 1 _x000a_(Modelo de Negocio)" dataDxfId="154"/>
+    <tableColumn id="20" name="Líder Técnico" dataDxfId="153"/>
+    <tableColumn id="21" name="Fecha Inicio" dataDxfId="152"/>
+    <tableColumn id="22" name="Fecha Fin" dataDxfId="151"/>
+    <tableColumn id="23" name="% Avance Planificado" dataDxfId="150"/>
+    <tableColumn id="24" name="% Avance ejecutado" dataDxfId="149"/>
+    <tableColumn id="25" name="Desv. %" dataDxfId="148">
       <calculatedColumnFormula>Tabla3[[#This Row],[% Avance ejecutado]]-Tabla3[[#This Row],[% Avance Planificado]]/Tabla3[[#This Row],[% Avance Planificado]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" name="Estado" dataDxfId="146"/>
-    <tableColumn id="27" name="SEGUIMIENTO  _x000a_(Planeamiento y Control de Gestión)" dataDxfId="145"/>
+    <tableColumn id="26" name="Estado" dataDxfId="147"/>
+    <tableColumn id="27" name="SEGUIMIENTO  _x000a_(Planeamiento y Control de Gestión)" dataDxfId="146"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14100,8 +14194,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="DemandaEstrateg_" displayName="DemandaEstrateg_" ref="A4:AV84" totalsRowShown="0" headerRowDxfId="141" dataDxfId="140" tableBorderDxfId="139">
-  <autoFilter ref="A4:AV84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="DemandaEstrateg_" displayName="DemandaEstrateg_" ref="A4:AV85" totalsRowShown="0" headerRowDxfId="141" dataDxfId="140" tableBorderDxfId="139">
+  <autoFilter ref="A4:AV85">
+    <filterColumn colId="36">
+      <filters>
+        <filter val="0%"/>
+        <filter val="100%"/>
+        <filter val="27%"/>
+        <filter val="38%"/>
+        <filter val="48%"/>
+        <filter val="58%"/>
+        <filter val="71%"/>
+        <filter val="86%"/>
+        <filter val="87%"/>
+        <filter val="88%"/>
+        <filter val="90%"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="48">
     <tableColumn id="23" name="ID" dataDxfId="138"/>
     <tableColumn id="38" name="ID Trámite" dataDxfId="137"/>
@@ -14694,7 +14804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75">
         <v>1</v>
       </c>
@@ -14793,7 +14903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75">
         <v>2</v>
       </c>
@@ -14890,7 +15000,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="75">
         <v>3</v>
       </c>
@@ -14987,7 +15097,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="75">
         <v>4</v>
       </c>
@@ -15084,7 +15194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="75">
         <v>5</v>
       </c>
@@ -15183,7 +15293,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="75">
         <v>6</v>
       </c>
@@ -15280,7 +15390,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
         <v>7</v>
       </c>
@@ -15377,7 +15487,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="75">
         <v>8</v>
       </c>
@@ -15467,7 +15577,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="75">
         <v>9</v>
       </c>
@@ -15553,7 +15663,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="75">
         <v>10</v>
       </c>
@@ -15652,7 +15762,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="75">
         <v>11</v>
       </c>
@@ -15747,7 +15857,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="75">
         <v>12</v>
       </c>
@@ -15842,7 +15952,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="75">
         <v>13</v>
       </c>
@@ -15937,7 +16047,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="75">
         <v>14</v>
       </c>
@@ -16032,7 +16142,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="75">
         <v>15</v>
       </c>
@@ -16122,7 +16232,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="75">
         <v>16</v>
       </c>
@@ -16212,7 +16322,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75">
         <v>17</v>
       </c>
@@ -16298,7 +16408,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
         <v>18</v>
       </c>
@@ -16395,7 +16505,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="75">
         <v>19</v>
       </c>
@@ -16484,7 +16594,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="75">
         <v>20</v>
       </c>
@@ -16581,7 +16691,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="75">
         <v>21</v>
       </c>
@@ -16678,7 +16788,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="75">
         <v>22</v>
       </c>
@@ -16775,7 +16885,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="75">
         <v>23</v>
       </c>
@@ -16872,7 +16982,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="75">
         <v>24</v>
       </c>
@@ -16955,7 +17065,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="75">
         <v>25</v>
       </c>
@@ -17038,7 +17148,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="75">
         <v>26</v>
       </c>
@@ -17133,7 +17243,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="75">
         <v>27</v>
       </c>
@@ -17222,7 +17332,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
         <v>28</v>
       </c>
@@ -17311,7 +17421,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="75">
         <v>29</v>
       </c>
@@ -17402,7 +17512,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="75">
         <v>30</v>
       </c>
@@ -17492,7 +17602,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="75">
         <v>31</v>
       </c>
@@ -17580,7 +17690,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="75">
         <v>32</v>
       </c>
@@ -17670,7 +17780,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="80.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="75">
         <v>33</v>
       </c>
@@ -17760,7 +17870,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="75">
         <v>34</v>
       </c>
@@ -17850,7 +17960,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="75">
         <v>35</v>
       </c>
@@ -17936,7 +18046,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="75">
         <v>36</v>
       </c>
@@ -18112,7 +18222,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="75">
         <v>38</v>
       </c>
@@ -18202,7 +18312,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="75">
         <v>39</v>
       </c>
@@ -18293,7 +18403,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="89">
         <v>40</v>
       </c>
@@ -18388,7 +18498,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="89">
         <v>41</v>
       </c>
@@ -18573,19 +18683,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" s="199" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="508" t="s">
+      <c r="A1" s="526" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="508"/>
+      <c r="B1" s="526"/>
       <c r="C1" s="197">
         <f>COUNT(DemandaEstrateg_[ID])</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" s="334"/>
       <c r="E1" s="334"/>
       <c r="F1" s="286">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="G1" s="204"/>
       <c r="H1" s="200"/>
@@ -18629,16 +18739,16 @@
       <c r="AU1" s="203"/>
     </row>
     <row r="2" spans="1:48" s="196" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="509" t="s">
+      <c r="A2" s="527" t="s">
         <v>310</v>
       </c>
-      <c r="B2" s="509"/>
-      <c r="C2" s="509"/>
-      <c r="D2" s="509"/>
-      <c r="E2" s="509"/>
-      <c r="F2" s="509"/>
-      <c r="G2" s="509"/>
-      <c r="H2" s="509"/>
+      <c r="B2" s="527"/>
+      <c r="C2" s="527"/>
+      <c r="D2" s="527"/>
+      <c r="E2" s="527"/>
+      <c r="F2" s="527"/>
+      <c r="G2" s="527"/>
+      <c r="H2" s="527"/>
       <c r="I2" s="193"/>
       <c r="J2" s="193"/>
       <c r="K2" s="193"/>
@@ -18847,7 +18957,7 @@
       <c r="AS4" s="217" t="s">
         <v>344</v>
       </c>
-      <c r="AT4" s="523" t="s">
+      <c r="AT4" s="508" t="s">
         <v>345</v>
       </c>
       <c r="AU4" s="217" t="s">
@@ -19014,7 +19124,7 @@
         <v>PROPLAFT-EO08-23-13</v>
       </c>
     </row>
-    <row r="6" spans="1:48" s="210" customFormat="1" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" s="210" customFormat="1" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55">
         <v>1323</v>
       </c>
@@ -19161,7 +19271,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55">
         <v>1741</v>
       </c>
@@ -19308,7 +19418,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:48" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" ht="54" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55">
         <v>1743</v>
       </c>
@@ -19455,7 +19565,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:48" s="210" customFormat="1" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" s="210" customFormat="1" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="163">
         <v>1749</v>
       </c>
@@ -19602,7 +19712,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="163">
         <v>1751</v>
       </c>
@@ -19749,7 +19859,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="163">
         <v>1752</v>
       </c>
@@ -19896,7 +20006,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:48" s="210" customFormat="1" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" s="210" customFormat="1" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="163">
         <v>1753</v>
       </c>
@@ -20045,7 +20155,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="163">
         <v>1755</v>
       </c>
@@ -20812,7 +20922,7 @@
         <v>PROKDD-EO05-23-4</v>
       </c>
     </row>
-    <row r="18" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
         <v>2250</v>
       </c>
@@ -20959,7 +21069,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
         <v>2264</v>
       </c>
@@ -21104,7 +21214,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
         <v>2265</v>
       </c>
@@ -21250,7 +21360,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="21" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
         <v>2288</v>
       </c>
@@ -21703,7 +21813,7 @@
         <v>PROTAIT-EO10-24-36</v>
       </c>
     </row>
-    <row r="24" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="55">
         <v>2340</v>
       </c>
@@ -21850,7 +21960,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="55">
         <v>2353</v>
       </c>
@@ -21999,7 +22109,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="55">
         <v>2400</v>
       </c>
@@ -22146,7 +22256,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="55">
         <v>2401</v>
       </c>
@@ -22293,7 +22403,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="163">
         <v>2405</v>
       </c>
@@ -22440,7 +22550,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="55">
         <v>2314</v>
       </c>
@@ -22597,7 +22707,7 @@
         <v>PROTTES-EO04-24-34</v>
       </c>
     </row>
-    <row r="30" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="55">
         <v>2458</v>
       </c>
@@ -22738,7 +22848,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="31" spans="1:48" s="212" customFormat="1" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" s="212" customFormat="1" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="163">
         <v>2487</v>
       </c>
@@ -22885,7 +22995,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" spans="1:48" s="212" customFormat="1" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" s="212" customFormat="1" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="163">
         <v>2488</v>
       </c>
@@ -23032,7 +23142,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="55">
         <v>2502</v>
       </c>
@@ -23329,7 +23439,7 @@
         <v>PRORPA-EO08-23-27</v>
       </c>
     </row>
-    <row r="35" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="55">
         <v>2510</v>
       </c>
@@ -23470,7 +23580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="55">
         <v>2541</v>
       </c>
@@ -23617,7 +23727,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="37" spans="1:48" s="109" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" s="109" customFormat="1" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="55">
         <v>2567</v>
       </c>
@@ -23758,7 +23868,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:48" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="55">
         <v>2568</v>
       </c>
@@ -23899,7 +24009,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:48" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="55">
         <v>2569</v>
       </c>
@@ -24040,7 +24150,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:48" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="55">
         <v>2570</v>
       </c>
@@ -24181,7 +24291,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="55">
         <v>2578</v>
       </c>
@@ -24322,7 +24432,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55">
         <v>2582</v>
       </c>
@@ -24468,7 +24578,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="55">
         <v>2605</v>
       </c>
@@ -24609,7 +24719,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="55">
         <v>2606</v>
       </c>
@@ -24758,7 +24868,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="55">
         <v>2608</v>
       </c>
@@ -24905,7 +25015,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="55">
         <v>2611</v>
       </c>
@@ -25052,7 +25162,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="55">
         <v>2612</v>
       </c>
@@ -25655,7 +25765,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:48" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="55">
         <v>2699</v>
       </c>
@@ -25796,7 +25906,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="55">
         <v>2702</v>
       </c>
@@ -25937,7 +26047,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="55">
         <v>2723</v>
       </c>
@@ -26086,7 +26196,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="55">
         <v>2728</v>
       </c>
@@ -26390,7 +26500,7 @@
         <v>PROBEFC-EO06-25-40</v>
       </c>
     </row>
-    <row r="56" spans="1:48" ht="49.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:48" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="55">
         <v>2779</v>
       </c>
@@ -26531,7 +26641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="55">
         <v>2790</v>
       </c>
@@ -26679,7 +26789,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="55">
         <v>2804</v>
       </c>
@@ -26979,7 +27089,7 @@
         <v>PROPBMBI-EO10-24-36</v>
       </c>
     </row>
-    <row r="60" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="55">
         <v>2859</v>
       </c>
@@ -27285,7 +27395,7 @@
         <v>PROASAHEH-EO10-25-41</v>
       </c>
     </row>
-    <row r="62" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="55">
         <v>2882</v>
       </c>
@@ -27432,7 +27542,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="55">
         <v>2883</v>
       </c>
@@ -27579,7 +27689,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="55">
         <v>2884</v>
       </c>
@@ -27726,7 +27836,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="55">
         <v>2885</v>
       </c>
@@ -27871,7 +27981,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="55">
         <v>2886</v>
       </c>
@@ -28018,7 +28128,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="55">
         <v>2887</v>
       </c>
@@ -28163,7 +28273,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="1:48" ht="49.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:48" ht="49.9" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="55">
         <v>2900</v>
       </c>
@@ -28309,7 +28419,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" spans="1:48" ht="51" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:48" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="298">
         <v>2951</v>
       </c>
@@ -28584,7 +28694,7 @@
         <v>PROEDDO-EO07-25-42</v>
       </c>
     </row>
-    <row r="71" spans="1:48" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:48" ht="78.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="298">
         <v>2839</v>
       </c>
@@ -28725,7 +28835,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="72" spans="1:48" ht="90" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:48" ht="90" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="298">
         <v>2901</v>
       </c>
@@ -29004,7 +29114,7 @@
         <v>PRONCR-EO05-23-5</v>
       </c>
     </row>
-    <row r="74" spans="1:48" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:48" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="298">
         <v>3034</v>
       </c>
@@ -29249,7 +29359,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="76" spans="1:48" s="109" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:48" s="109" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="298">
         <v>3099</v>
       </c>
@@ -29353,7 +29463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:48" s="109" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:48" s="109" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="298">
         <v>3100</v>
       </c>
@@ -29574,7 +29684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:48" s="109" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:48" s="109" customFormat="1" ht="45" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="426">
         <v>3102</v>
       </c>
@@ -29687,7 +29797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:48" s="109" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:48" s="109" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="426">
         <v>3105</v>
       </c>
@@ -29806,7 +29916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:48" s="109" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:48" s="109" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="298">
         <v>3124</v>
       </c>
@@ -29922,7 +30032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:48" s="109" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:48" s="109" customFormat="1" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="298">
         <v>3142</v>
       </c>
@@ -30032,7 +30142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:48" s="109" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:48" s="109" customFormat="1" ht="45" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="298">
         <v>3151</v>
       </c>
@@ -30142,7 +30252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:48" s="109" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:48" s="109" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="298">
         <v>3259</v>
       </c>
@@ -30291,22 +30401,120 @@
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:48" s="109" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
-      <c r="E85" s="57"/>
-      <c r="F85" s="209"/>
-      <c r="G85" s="209"/>
-      <c r="H85" s="62"/>
-      <c r="I85" s="62"/>
-      <c r="J85" s="62"/>
-      <c r="K85" s="62"/>
-      <c r="L85" s="117"/>
-      <c r="Q85" s="57"/>
-      <c r="AB85" s="62"/>
-      <c r="AC85" s="62"/>
-      <c r="AG85" s="57"/>
-      <c r="AR85" s="111"/>
-      <c r="AU85" s="118"/>
+    <row r="85" spans="1:48" s="109" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="510">
+        <v>532453</v>
+      </c>
+      <c r="B85" s="511" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C85" s="511">
+        <v>2509</v>
+      </c>
+      <c r="D85" s="511" t="s">
+        <v>779</v>
+      </c>
+      <c r="E85" s="512" t="s">
+        <v>347</v>
+      </c>
+      <c r="F85" s="513" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G85" s="514"/>
+      <c r="H85" s="512" t="s">
+        <v>128</v>
+      </c>
+      <c r="I85" s="512" t="s">
+        <v>781</v>
+      </c>
+      <c r="J85" s="515"/>
+      <c r="K85" s="516"/>
+      <c r="L85" s="517"/>
+      <c r="M85" s="518" t="s">
+        <v>370</v>
+      </c>
+      <c r="N85" s="511"/>
+      <c r="O85" s="519"/>
+      <c r="P85" s="520"/>
+      <c r="Q85" s="511"/>
+      <c r="R85" s="511"/>
+      <c r="S85" s="511"/>
+      <c r="T85" s="521"/>
+      <c r="U85" s="522">
+        <v>0</v>
+      </c>
+      <c r="V85" s="522">
+        <v>0</v>
+      </c>
+      <c r="W85" s="523"/>
+      <c r="X85" s="523"/>
+      <c r="Y85" s="517" t="s">
+        <v>1492</v>
+      </c>
+      <c r="Z85" s="517" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA85" s="518"/>
+      <c r="AB85" s="511" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC85" s="511" t="s">
+        <v>454</v>
+      </c>
+      <c r="AD85" s="511" t="s">
+        <v>782</v>
+      </c>
+      <c r="AE85" s="511" t="s">
+        <v>783</v>
+      </c>
+      <c r="AF85" s="437">
+        <v>45895</v>
+      </c>
+      <c r="AG85" s="438">
+        <v>46021</v>
+      </c>
+      <c r="AH85" s="471">
+        <v>46037</v>
+      </c>
+      <c r="AI85" s="439">
+        <v>1</v>
+      </c>
+      <c r="AJ85" s="439">
+        <v>0.99</v>
+      </c>
+      <c r="AK85" s="440" t="s">
+        <v>373</v>
+      </c>
+      <c r="AL85" s="441" t="s">
+        <v>373</v>
+      </c>
+      <c r="AM85" s="191"/>
+      <c r="AN85" s="290">
+        <v>46021</v>
+      </c>
+      <c r="AO85" s="153" t="s">
+        <v>421</v>
+      </c>
+      <c r="AP85" s="461" t="s">
+        <v>422</v>
+      </c>
+      <c r="AQ85" s="384" t="s">
+        <v>528</v>
+      </c>
+      <c r="AR85" s="152" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS85" s="443" t="s">
+        <v>784</v>
+      </c>
+      <c r="AT85" s="112">
+        <v>0</v>
+      </c>
+      <c r="AU85" s="524"/>
+      <c r="AV85" s="525">
+        <f>'Portafolio P&amp;D'!B91</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:48" s="109" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="57"/>
@@ -30424,6 +30632,8 @@
       <c r="AB92" s="62"/>
       <c r="AC92" s="62"/>
       <c r="AG92" s="57"/>
+      <c r="AK92" s="509"/>
+      <c r="AL92" s="509"/>
       <c r="AR92" s="111"/>
       <c r="AU92" s="118"/>
     </row>
@@ -34974,10 +35184,10 @@
   </mergeCells>
   <phoneticPr fontId="50" type="noConversion"/>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="144" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN6">
-    <cfRule type="iconSet" priority="10">
+    <cfRule type="iconSet" priority="12">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -34986,10 +35196,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="143" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO21:AP21 AO35:AP35 AO34 AO56:AP57 AO5:AO20 AO33:AP33 AO31:AO32 AO37:AP41 AO36 AO51:AP52 AO44:AO50 AO30:AP30 AO22:AO29 AO43:AP43 AO42 AO53:AO55 AO58:AO68">
-    <cfRule type="iconSet" priority="1644">
+    <cfRule type="iconSet" priority="1646">
       <iconSet showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="-0.1"/>
@@ -34998,7 +35208,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM84">
-    <cfRule type="iconSet" priority="1696">
+    <cfRule type="iconSet" priority="1698">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -35006,11 +35216,11 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A84">
-    <cfRule type="duplicateValues" dxfId="142" priority="1698"/>
+  <conditionalFormatting sqref="A5:A85">
+    <cfRule type="duplicateValues" dxfId="143" priority="1700"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO84">
-    <cfRule type="iconSet" priority="1">
+    <cfRule type="iconSet" priority="3">
       <iconSet showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="-0.1"/>
@@ -35018,11 +35228,23 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A85">
+    <cfRule type="duplicateValues" dxfId="142" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK85">
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 E15:E17 E34 E48:E49 E73 E55 E59 E61 E29 E22:E23">
       <formula1>"Proyecto, Heredado"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS76:AS77 AS74 AS18:AS21 AS24:AS28 AS30:AS33 AG14:AG31 AS35:AS47 AS51:AS54 AS56:AS58 AS60 AS62:AS69 AG5:AG12 AS6:AS14 H5:H84 AS84"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS76:AS77 AS74 AS18:AS21 AS24:AS28 AS30:AS33 AG14:AG31 AS35:AS47 AS51:AS54 AS56:AS58 AS60 AS62:AS69 AG5:AG12 AS6:AS14 H5:H85 AS84"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E74 E18:E21 E24:E33 E35:E47 E50:E54 E56:E58 E60 E62:E72 E6:E14">
       <formula1>"Proyecto, Proyecto-Hijo"</formula1>
     </dataValidation>
@@ -35049,43 +35271,43 @@
           <x14:formula1>
             <xm:f>Definiciones!$A$225:$A$237</xm:f>
           </x14:formula1>
-          <xm:sqref>P5:P79 P84</xm:sqref>
+          <xm:sqref>P5:P79 P84:P85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$205:$A$222</xm:f>
           </x14:formula1>
-          <xm:sqref>P80 O5:O80 O81:P83 O84</xm:sqref>
+          <xm:sqref>P80 O5:O80 O81:P83 O84:O85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$186:$A$202</xm:f>
           </x14:formula1>
-          <xm:sqref>N5:N84</xm:sqref>
+          <xm:sqref>N5:N85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$64:$A$69</xm:f>
           </x14:formula1>
-          <xm:sqref>Q5:Q84</xm:sqref>
+          <xm:sqref>Q5:Q85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$72:$A$83</xm:f>
           </x14:formula1>
-          <xm:sqref>R5:R84</xm:sqref>
+          <xm:sqref>R5:R85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$240:$A$354</xm:f>
           </x14:formula1>
-          <xm:sqref>AA5:AA84</xm:sqref>
+          <xm:sqref>AA5:AA85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definiciones!$A$86:$A$92</xm:f>
           </x14:formula1>
-          <xm:sqref>Z5:Z84</xm:sqref>
+          <xm:sqref>Z5:Z85</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -35095,7 +35317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -35127,110 +35349,110 @@
   <sheetData>
     <row r="2" spans="2:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="N2" s="57"/>
-      <c r="O2" s="511" t="s">
+      <c r="O2" s="529" t="s">
         <v>813</v>
       </c>
-      <c r="P2" s="512"/>
-      <c r="Q2" s="511" t="s">
+      <c r="P2" s="530"/>
+      <c r="Q2" s="529" t="s">
         <v>814</v>
       </c>
-      <c r="R2" s="512"/>
-      <c r="S2" s="511" t="s">
+      <c r="R2" s="530"/>
+      <c r="S2" s="529" t="s">
         <v>815</v>
       </c>
-      <c r="T2" s="512"/>
-      <c r="U2" s="511" t="s">
+      <c r="T2" s="530"/>
+      <c r="U2" s="529" t="s">
         <v>816</v>
       </c>
-      <c r="V2" s="512"/>
-      <c r="W2" s="511" t="s">
+      <c r="V2" s="530"/>
+      <c r="W2" s="529" t="s">
         <v>817</v>
       </c>
-      <c r="X2" s="512"/>
-      <c r="Y2" s="511" t="s">
+      <c r="X2" s="530"/>
+      <c r="Y2" s="529" t="s">
         <v>818</v>
       </c>
-      <c r="Z2" s="512"/>
-      <c r="AA2" s="511" t="s">
+      <c r="Z2" s="530"/>
+      <c r="AA2" s="529" t="s">
         <v>819</v>
       </c>
-      <c r="AB2" s="512"/>
-      <c r="AC2" s="511" t="s">
+      <c r="AB2" s="530"/>
+      <c r="AC2" s="529" t="s">
         <v>820</v>
       </c>
-      <c r="AD2" s="512"/>
-      <c r="AE2" s="511" t="s">
+      <c r="AD2" s="530"/>
+      <c r="AE2" s="529" t="s">
         <v>821</v>
       </c>
-      <c r="AF2" s="512"/>
-      <c r="AG2" s="511" t="s">
+      <c r="AF2" s="530"/>
+      <c r="AG2" s="529" t="s">
         <v>822</v>
       </c>
-      <c r="AH2" s="512"/>
-      <c r="AI2" s="511" t="s">
+      <c r="AH2" s="530"/>
+      <c r="AI2" s="529" t="s">
         <v>823</v>
       </c>
-      <c r="AJ2" s="512"/>
-      <c r="AK2" s="511" t="s">
+      <c r="AJ2" s="530"/>
+      <c r="AK2" s="529" t="s">
         <v>824</v>
       </c>
-      <c r="AL2" s="512"/>
-      <c r="AM2" s="513" t="s">
+      <c r="AL2" s="530"/>
+      <c r="AM2" s="531" t="s">
         <v>825</v>
       </c>
-      <c r="AN2" s="515"/>
-      <c r="AO2" s="513" t="s">
+      <c r="AN2" s="533"/>
+      <c r="AO2" s="531" t="s">
         <v>826</v>
       </c>
-      <c r="AP2" s="515"/>
-      <c r="AQ2" s="513" t="s">
+      <c r="AP2" s="533"/>
+      <c r="AQ2" s="531" t="s">
         <v>827</v>
       </c>
-      <c r="AR2" s="515"/>
-      <c r="AS2" s="513" t="s">
+      <c r="AR2" s="533"/>
+      <c r="AS2" s="531" t="s">
         <v>828</v>
       </c>
-      <c r="AT2" s="515"/>
-      <c r="AU2" s="513" t="s">
+      <c r="AT2" s="533"/>
+      <c r="AU2" s="531" t="s">
         <v>829</v>
       </c>
-      <c r="AV2" s="515"/>
-      <c r="AW2" s="513" t="s">
+      <c r="AV2" s="533"/>
+      <c r="AW2" s="531" t="s">
         <v>830</v>
       </c>
-      <c r="AX2" s="515"/>
-      <c r="AY2" s="513" t="s">
+      <c r="AX2" s="533"/>
+      <c r="AY2" s="531" t="s">
         <v>831</v>
       </c>
-      <c r="AZ2" s="515"/>
-      <c r="BA2" s="513" t="s">
+      <c r="AZ2" s="533"/>
+      <c r="BA2" s="531" t="s">
         <v>832</v>
       </c>
-      <c r="BB2" s="515"/>
-      <c r="BC2" s="513" t="s">
+      <c r="BB2" s="533"/>
+      <c r="BC2" s="531" t="s">
         <v>833</v>
       </c>
-      <c r="BD2" s="515"/>
-      <c r="BE2" s="513" t="s">
+      <c r="BD2" s="533"/>
+      <c r="BE2" s="531" t="s">
         <v>834</v>
       </c>
-      <c r="BF2" s="515"/>
-      <c r="BG2" s="513" t="s">
+      <c r="BF2" s="533"/>
+      <c r="BG2" s="531" t="s">
         <v>835</v>
       </c>
-      <c r="BH2" s="515"/>
-      <c r="BI2" s="513" t="s">
+      <c r="BH2" s="533"/>
+      <c r="BI2" s="531" t="s">
         <v>836</v>
       </c>
-      <c r="BJ2" s="514"/>
-      <c r="BK2" s="510" t="s">
+      <c r="BJ2" s="532"/>
+      <c r="BK2" s="528" t="s">
         <v>837</v>
       </c>
-      <c r="BL2" s="510"/>
-      <c r="BM2" s="510" t="s">
+      <c r="BL2" s="528"/>
+      <c r="BM2" s="528" t="s">
         <v>838</v>
       </c>
-      <c r="BN2" s="510"/>
+      <c r="BN2" s="528"/>
     </row>
     <row r="3" spans="2:67" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B3" s="121" t="s">
@@ -35432,7 +35654,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="4" spans="2:67" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:67" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="133"/>
       <c r="C4" s="135" t="str">
         <f>'Portafolio P&amp;D'!B3</f>
@@ -35533,7 +35755,7 @@
       <c r="BN4" s="141"/>
       <c r="BO4" s="341"/>
     </row>
-    <row r="5" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:67" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="128"/>
       <c r="C5" s="129" t="str">
         <f>'Portafolio P&amp;D'!B4</f>
@@ -35634,7 +35856,7 @@
       <c r="BN5" s="131"/>
       <c r="BO5" s="132"/>
     </row>
-    <row r="6" spans="2:67" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:67" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="133">
         <v>1</v>
       </c>
@@ -35846,7 +36068,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="7" spans="2:67" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:67" ht="80.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="128">
         <v>2</v>
       </c>
@@ -36057,7 +36279,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="8" spans="2:67" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:67" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="133"/>
       <c r="C8" s="135" t="str">
         <f>'Portafolio P&amp;D'!B5</f>
@@ -36158,7 +36380,7 @@
       <c r="BN8" s="141"/>
       <c r="BO8" s="341"/>
     </row>
-    <row r="9" spans="2:67" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:67" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="128"/>
       <c r="C9" s="129" t="str">
         <f>'Portafolio P&amp;D'!B6</f>
@@ -36259,7 +36481,7 @@
       <c r="BN9" s="131"/>
       <c r="BO9" s="132"/>
     </row>
-    <row r="10" spans="2:67" ht="216.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:67" ht="216.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="B10" s="133">
         <v>3</v>
       </c>
@@ -36470,7 +36692,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="11" spans="2:67" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:67" ht="120.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="128">
         <v>4</v>
       </c>
@@ -36681,7 +36903,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="12" spans="2:67" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:67" ht="78.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="133">
         <v>5</v>
       </c>
@@ -36892,7 +37114,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="13" spans="2:67" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:67" ht="80.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="128">
         <v>6</v>
       </c>
@@ -37103,7 +37325,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="14" spans="2:67" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:67" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="133">
         <v>7</v>
       </c>
@@ -37314,7 +37536,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="15" spans="2:67" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:67" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="128">
         <v>8</v>
       </c>
@@ -37525,7 +37747,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="16" spans="2:67" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:67" ht="78.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="133">
         <v>9</v>
       </c>
@@ -37736,7 +37958,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="17" spans="2:67" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:67" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="128">
         <v>10</v>
       </c>
@@ -37947,7 +38169,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="18" spans="2:67" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:67" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="133">
         <v>11</v>
       </c>
@@ -38158,7 +38380,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="19" spans="2:67" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:67" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="128">
         <v>12</v>
       </c>
@@ -38369,7 +38591,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="20" spans="2:67" ht="93.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:67" ht="93.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="133">
         <v>13</v>
       </c>
@@ -38580,7 +38802,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="21" spans="2:67" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:67" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="128"/>
       <c r="C21" s="129" t="str">
         <f>'Portafolio P&amp;D'!B15</f>
@@ -38683,7 +38905,7 @@
       <c r="BN21" s="131"/>
       <c r="BO21" s="132"/>
     </row>
-    <row r="22" spans="2:67" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:67" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="133"/>
       <c r="C22" s="135" t="str">
         <f>'Portafolio P&amp;D'!B21</f>
@@ -38784,7 +39006,7 @@
       <c r="BN22" s="141"/>
       <c r="BO22" s="341"/>
     </row>
-    <row r="23" spans="2:67" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:67" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="128">
         <v>14</v>
       </c>
@@ -38993,7 +39215,7 @@
       </c>
       <c r="BO23" s="143"/>
     </row>
-    <row r="24" spans="2:67" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:67" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="133">
         <v>15</v>
       </c>
@@ -39204,7 +39426,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="25" spans="2:67" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:67" ht="66" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="128">
         <v>16</v>
       </c>
@@ -39415,7 +39637,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="26" spans="2:67" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:67" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="133">
         <v>17</v>
       </c>
@@ -39626,7 +39848,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="27" spans="2:67" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:67" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="128">
         <v>18</v>
       </c>
@@ -39837,7 +40059,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="28" spans="2:67" ht="132.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:67" ht="132.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="133">
         <v>19</v>
       </c>
@@ -40048,7 +40270,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="29" spans="2:67" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:67" ht="62.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="128">
         <v>20</v>
       </c>
@@ -40259,7 +40481,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="30" spans="2:67" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:67" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="133"/>
       <c r="C30" s="135" t="str">
         <f>'Portafolio P&amp;D'!B30</f>
@@ -40677,7 +40899,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="32" spans="2:67" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:67" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="133">
         <v>22</v>
       </c>
@@ -40888,7 +41110,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="33" spans="2:67" ht="114.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:67" ht="114.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="B33" s="128">
         <v>23</v>
       </c>
@@ -41099,7 +41321,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="34" spans="2:67" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:67" ht="111" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="133">
         <v>24</v>
       </c>
@@ -41310,7 +41532,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="35" spans="2:67" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:67" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="128">
         <v>25</v>
       </c>
@@ -41521,7 +41743,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="36" spans="2:67" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:67" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="133">
         <v>26</v>
       </c>
@@ -41761,7 +41983,18 @@
       <c r="M40" s="64"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:BO36"/>
+  <autoFilter ref="B3:BO36">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="02. En Curso"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="26">
     <mergeCell ref="AO2:AP2"/>
     <mergeCell ref="BA2:BB2"/>
@@ -44541,27 +44774,27 @@
       </c>
       <c r="C1" s="27">
         <f ca="1">TODAY()</f>
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" s="323"/>
-      <c r="H2" s="520"/>
-      <c r="I2" s="520"/>
-      <c r="J2" s="520"/>
-      <c r="N2" s="519" t="s">
+      <c r="H2" s="538"/>
+      <c r="I2" s="538"/>
+      <c r="J2" s="538"/>
+      <c r="N2" s="537" t="s">
         <v>1066</v>
       </c>
-      <c r="O2" s="519"/>
-      <c r="P2" s="519"/>
-      <c r="Q2" s="519"/>
-      <c r="R2" s="519"/>
-      <c r="S2" s="519"/>
-      <c r="T2" s="519"/>
-      <c r="U2" s="519"/>
-      <c r="V2" s="519"/>
-      <c r="W2" s="519"/>
-      <c r="X2" s="519"/>
+      <c r="O2" s="537"/>
+      <c r="P2" s="537"/>
+      <c r="Q2" s="537"/>
+      <c r="R2" s="537"/>
+      <c r="S2" s="537"/>
+      <c r="T2" s="537"/>
+      <c r="U2" s="537"/>
+      <c r="V2" s="537"/>
+      <c r="W2" s="537"/>
+      <c r="X2" s="537"/>
     </row>
     <row r="3" spans="1:29" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -44636,7 +44869,7 @@
       </c>
     </row>
     <row r="4" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="516" t="s">
+      <c r="A4" s="534" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="22">
@@ -44675,7 +44908,7 @@
       </c>
       <c r="L4" s="17">
         <f t="shared" ref="L4:L17" ca="1" si="0">H4-$C$1</f>
-        <v>-422</v>
+        <v>-425</v>
       </c>
       <c r="M4" s="31" t="str">
         <f t="shared" ref="M4:M17" ca="1" si="1">IF(L4&lt;=0,$AB$4,IF(L4&lt;=H4,$AB$6,$AB$5))</f>
@@ -44705,7 +44938,7 @@
       </c>
     </row>
     <row r="5" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="517"/>
+      <c r="A5" s="535"/>
       <c r="B5" s="22">
         <v>2</v>
       </c>
@@ -44742,7 +44975,7 @@
       </c>
       <c r="L5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-116</v>
+        <v>-119</v>
       </c>
       <c r="M5" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -44774,7 +45007,7 @@
       </c>
     </row>
     <row r="6" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="517"/>
+      <c r="A6" s="535"/>
       <c r="B6" s="22">
         <v>3</v>
       </c>
@@ -44811,7 +45044,7 @@
       </c>
       <c r="L6" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-177</v>
+        <v>-180</v>
       </c>
       <c r="M6" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -44845,7 +45078,7 @@
       </c>
     </row>
     <row r="7" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="517"/>
+      <c r="A7" s="535"/>
       <c r="B7" s="22">
         <v>4</v>
       </c>
@@ -44882,7 +45115,7 @@
       </c>
       <c r="L7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M7" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -44908,7 +45141,7 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="518"/>
+      <c r="A8" s="536"/>
       <c r="B8" s="22">
         <v>5</v>
       </c>
@@ -44945,7 +45178,7 @@
       </c>
       <c r="L8" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M8" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -44971,7 +45204,7 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="516" t="s">
+      <c r="A9" s="534" t="s">
         <v>128</v>
       </c>
       <c r="B9" s="22">
@@ -45010,7 +45243,7 @@
       </c>
       <c r="L9" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-330</v>
+        <v>-333</v>
       </c>
       <c r="M9" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45034,7 +45267,7 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="517"/>
+      <c r="A10" s="535"/>
       <c r="B10" s="22">
         <v>7</v>
       </c>
@@ -45071,7 +45304,7 @@
       </c>
       <c r="L10" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-57</v>
+        <v>-60</v>
       </c>
       <c r="M10" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45099,7 +45332,7 @@
       </c>
     </row>
     <row r="11" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="518"/>
+      <c r="A11" s="536"/>
       <c r="B11" s="22">
         <v>8</v>
       </c>
@@ -45136,7 +45369,7 @@
       </c>
       <c r="L11" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-147</v>
+        <v>-150</v>
       </c>
       <c r="M11" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45201,7 +45434,7 @@
       </c>
       <c r="L12" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-391</v>
+        <v>-394</v>
       </c>
       <c r="M12" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45264,7 +45497,7 @@
       </c>
       <c r="L13" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-300</v>
+        <v>-303</v>
       </c>
       <c r="M13" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45327,7 +45560,7 @@
       </c>
       <c r="L14" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-330</v>
+        <v>-333</v>
       </c>
       <c r="M14" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45351,7 +45584,7 @@
       </c>
     </row>
     <row r="15" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="516" t="s">
+      <c r="A15" s="534" t="s">
         <v>1099</v>
       </c>
       <c r="B15" s="22">
@@ -45390,7 +45623,7 @@
       </c>
       <c r="L15" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-391</v>
+        <v>-394</v>
       </c>
       <c r="M15" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45414,7 +45647,7 @@
       </c>
     </row>
     <row r="16" spans="1:29" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="517"/>
+      <c r="A16" s="535"/>
       <c r="B16" s="22">
         <v>13</v>
       </c>
@@ -45451,7 +45684,7 @@
       </c>
       <c r="L16" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-300</v>
+        <v>-303</v>
       </c>
       <c r="M16" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -45475,7 +45708,7 @@
       </c>
     </row>
     <row r="17" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="518"/>
+      <c r="A17" s="536"/>
       <c r="B17" s="22">
         <v>14</v>
       </c>
@@ -45512,7 +45745,7 @@
       </c>
       <c r="L17" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>-147</v>
+        <v>-150</v>
       </c>
       <c r="M17" s="31" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -48562,15 +48795,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="521" t="s">
+      <c r="A2" s="539" t="s">
         <v>1461</v>
       </c>
-      <c r="B2" s="521"/>
-      <c r="C2" s="521"/>
-      <c r="D2" s="521"/>
-      <c r="E2" s="521"/>
-      <c r="F2" s="521"/>
-      <c r="G2" s="521"/>
+      <c r="B2" s="539"/>
+      <c r="C2" s="539"/>
+      <c r="D2" s="539"/>
+      <c r="E2" s="539"/>
+      <c r="F2" s="539"/>
+      <c r="G2" s="539"/>
     </row>
     <row r="4" spans="1:9" s="103" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="98" t="s">
@@ -48769,15 +49002,15 @@
       <c r="I11" s="288"/>
     </row>
     <row r="13" spans="1:9" s="97" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="522" t="s">
+      <c r="A13" s="540" t="s">
         <v>1482</v>
       </c>
-      <c r="B13" s="522"/>
-      <c r="C13" s="522"/>
-      <c r="D13" s="522"/>
-      <c r="E13" s="522"/>
-      <c r="F13" s="522"/>
-      <c r="G13" s="522"/>
+      <c r="B13" s="540"/>
+      <c r="C13" s="540"/>
+      <c r="D13" s="540"/>
+      <c r="E13" s="540"/>
+      <c r="F13" s="540"/>
+      <c r="G13" s="540"/>
     </row>
   </sheetData>
   <mergeCells count="2">
